--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/6655-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/6655-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C8C000AB-136C-47B6-B00F-BBAFF78C3348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{60D483BD-55F9-41C3-933A-19737297BDD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{6CEA682F-CB81-4E40-8F2A-73FF1B4C0E37}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{66A2631D-ABB8-4C1B-A028-3A305793099D}"/>
   </bookViews>
   <sheets>
     <sheet name="6655-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1478,21 +1478,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57A0CF47-5272-45A7-B949-241FDA6B185F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34110F82-9918-4A4F-8C9D-A6506BC68A48}">
   <dimension ref="A1:R24"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="5" width="8.33203125" customWidth="1"/>
-    <col min="6" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.77734375" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="5" width="10.5" customWidth="1"/>
+    <col min="6" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1520,7 +1520,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1550,7 +1550,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1596,7 +1596,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1646,7 +1646,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1700,7 +1700,7 @@
         <v>3.39</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1756,7 +1756,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1812,7 +1812,7 @@
         <v>2.36</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="39">
         <v>2024</v>
       </c>
@@ -1866,7 +1866,7 @@
         <v>8.64</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1922,7 +1922,7 @@
         <v>6.21</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>2.4300000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="37">
         <v>2023</v>
       </c>
@@ -2032,7 +2032,7 @@
         <v>4.72</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>25</v>
       </c>
@@ -2088,7 +2088,7 @@
         <v>4.72</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
@@ -2144,7 +2144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="39">
         <v>2022</v>
       </c>
@@ -2198,7 +2198,7 @@
         <v>3.46</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>25</v>
       </c>
@@ -2254,7 +2254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>25</v>
       </c>
@@ -2310,7 +2310,7 @@
         <v>3.46</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="37">
         <v>2021</v>
       </c>
@@ -2364,7 +2364,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2420,7 +2420,7 @@
         <v>8.93</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2476,7 +2476,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="39">
         <v>2020</v>
       </c>
@@ -2530,7 +2530,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="37">
         <v>2019</v>
       </c>
@@ -2584,7 +2584,7 @@
         <v>3.92</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="39">
         <v>2018</v>
       </c>
@@ -2638,7 +2638,7 @@
         <v>1.96</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="37">
         <v>2017</v>
       </c>
@@ -2692,7 +2692,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="39" t="s">
         <v>45</v>
       </c>
